--- a/BLAZAMLocalization/Blazam Translation.xlsx
+++ b/BLAZAMLocalization/Blazam Translation.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Chris\source\repos\Blazam-App\BLAZAM\BLAZAMLocalization\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{CA44CCBF-F51E-403D-8ECC-B44A9C7483F8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{43EEC1D6-185F-4AC4-95CA-220EBC78ECAC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="17625" yWindow="495" windowWidth="10035" windowHeight="13980" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Main Sheet" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4564" uniqueCount="3280">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4570" uniqueCount="3286">
   <si>
     <t>Key</t>
   </si>
@@ -9878,6 +9878,24 @@
   </si>
   <si>
     <t>Token Lifetime</t>
+  </si>
+  <si>
+    <t>Dismiss all</t>
+  </si>
+  <si>
+    <t>Notification Settings</t>
+  </si>
+  <si>
+    <t>No matching entries</t>
+  </si>
+  <si>
+    <t>Changed</t>
+  </si>
+  <si>
+    <t>Locked Out</t>
+  </si>
+  <si>
+    <t>Require Password Change</t>
   </si>
 </sst>
 </file>
@@ -10188,7 +10206,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:Z363"/>
+  <dimension ref="A1:Z369"/>
   <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
   <sheetData>
     <row r="1" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -22116,6 +22134,36 @@
     <row r="363" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A363" s="7" t="s">
         <v>3279</v>
+      </c>
+    </row>
+    <row r="364" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A364" t="s">
+        <v>3280</v>
+      </c>
+    </row>
+    <row r="365" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A365" t="s">
+        <v>3281</v>
+      </c>
+    </row>
+    <row r="366" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A366" s="7" t="s">
+        <v>3282</v>
+      </c>
+    </row>
+    <row r="367" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A367" t="s">
+        <v>3283</v>
+      </c>
+    </row>
+    <row r="368" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A368" t="s">
+        <v>3284</v>
+      </c>
+    </row>
+    <row r="369" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A369" t="s">
+        <v>3285</v>
       </c>
     </row>
   </sheetData>

--- a/BLAZAMLocalization/Blazam Translation.xlsx
+++ b/BLAZAMLocalization/Blazam Translation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Chris\source\repos\Blazam-App\BLAZAM\BLAZAMLocalization\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{43EEC1D6-185F-4AC4-95CA-220EBC78ECAC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C1167E06-5A14-4CE5-903A-D2BB27BE5C8E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="17625" yWindow="495" windowWidth="10035" windowHeight="13980" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4570" uniqueCount="3286">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4578" uniqueCount="3293">
   <si>
     <t>Key</t>
   </si>
@@ -9896,6 +9896,27 @@
   </si>
   <si>
     <t>Require Password Change</t>
+  </si>
+  <si>
+    <t>Last OU</t>
+  </si>
+  <si>
+    <t>Search Directory</t>
+  </si>
+  <si>
+    <t>Include Disabled</t>
+  </si>
+  <si>
+    <t>Manage Webhooks</t>
+  </si>
+  <si>
+    <t>Manage Notifications</t>
+  </si>
+  <si>
+    <t>Daily Users</t>
+  </si>
+  <si>
+    <t>Daily Logins</t>
   </si>
 </sst>
 </file>
@@ -10206,7 +10227,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:Z369"/>
+  <dimension ref="A1:Z377"/>
   <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
   <sheetData>
     <row r="1" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -22164,6 +22185,46 @@
     <row r="369" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A369" t="s">
         <v>3285</v>
+      </c>
+    </row>
+    <row r="370" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A370" s="7" t="s">
+        <v>2449</v>
+      </c>
+    </row>
+    <row r="371" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A371" s="7" t="s">
+        <v>3286</v>
+      </c>
+    </row>
+    <row r="372" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A372" t="s">
+        <v>3287</v>
+      </c>
+    </row>
+    <row r="373" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A373" t="s">
+        <v>3288</v>
+      </c>
+    </row>
+    <row r="374" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A374" t="s">
+        <v>3289</v>
+      </c>
+    </row>
+    <row r="375" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A375" s="7" t="s">
+        <v>3290</v>
+      </c>
+    </row>
+    <row r="376" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A376" s="7" t="s">
+        <v>3291</v>
+      </c>
+    </row>
+    <row r="377" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A377" s="7" t="s">
+        <v>3292</v>
       </c>
     </row>
   </sheetData>
@@ -26291,7 +26352,7 @@
       </c>
       <c r="B204" s="6">
         <f>COUNTIF('Main Sheet'!A:A,A204)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="205" spans="1:2" ht="15" x14ac:dyDescent="0.25">
